--- a/output/differences.xlsx
+++ b/output/differences.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Currency mismatch: {'USD', 'EUR'}</t>
+          <t>Currency mismatch: {'EUR', 'USD'}</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Scale mismatch: {'million', 'billion'}</t>
+          <t>Scale mismatch: {'billion', 'million'}</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">

--- a/output/differences.xlsx
+++ b/output/differences.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -499,11 +499,11 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Article 212 t</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -542,11 +542,11 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Article 2 o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -585,11 +585,11 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Article 32 o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -628,26 +628,26 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>135.0 EUR</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1.5 USD</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135.0 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CURRENCY_MISMATCH</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Currency mismatch: {'EUR', 'USD'}</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -671,26 +671,26 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>135.0 million</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1.5 billion</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135.0 million</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SCALE_ERROR</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Scale mismatch: {'billion', 'million'}</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -714,26 +714,26 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EUR 135 million</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,5 Mrd. USD</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>135 miljonu EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=135000000.0, DE=1500000000.0, LV=135000000.0</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -757,16 +757,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>136 Mio. EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Monetary value present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -800,11 +800,11 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Article 18(2) o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Article 6(2)</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -886,11 +886,11 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Article 19(3) f</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -929,11 +929,11 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Article 31(4) o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -972,16 +972,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>(EU, Eurato) 2024/2509</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>(EU, Euratom) 2024/2509</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1015,11 +1015,11 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Article 322 o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1058,11 +1058,11 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Article 19(2)</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1101,11 +1101,11 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Article 6(2)</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1144,11 +1144,11 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Article 214 o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1187,11 +1187,11 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Article 6(2)</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1230,11 +1230,11 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Article 31(5)</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1273,16 +1273,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>(EU, Euratom) No 883/2013</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>(EU, Euratom) Nr. 883/2013</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1316,16 +1316,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>(EU, Euratom) No 883/2013</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>(EU, Euratom) Nr. 883/2013</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1359,11 +1359,11 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Article 129 o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,11 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Article 6
-I</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1422,7 +1421,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1432,12 +1431,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1446,16 +1445,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,5 Mrd. EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1465,7 +1464,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1475,12 +1474,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Monetary value present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1489,11 +1488,11 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Article 31(4) o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1508,7 +1507,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1518,12 +1517,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1531,11 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Article 6(2)</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1551,7 +1550,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1561,12 +1560,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1575,11 +1574,11 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Article 18(2) a</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1594,7 +1593,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1604,12 +1603,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1618,11 +1617,11 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Article 19(3) f</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1637,7 +1636,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1647,12 +1646,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1661,11 +1660,11 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>paragraph 2</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1680,7 +1679,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1690,12 +1689,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1704,11 +1703,11 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>paragraph 6</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1723,7 +1722,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1733,12 +1732,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1747,11 +1746,11 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Article 32 o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1766,7 +1765,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1776,12 +1775,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1790,11 +1789,11 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Article 19 o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1809,7 +1808,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1819,12 +1818,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1833,11 +1832,11 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>paragraph 2</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1852,7 +1851,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1862,12 +1861,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1876,12 +1875,11 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Article 30
-E</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1896,7 +1894,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1906,12 +1904,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1920,16 +1918,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Article 272 T</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Art. 272 A</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1939,7 +1937,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1949,12 +1947,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1963,26 +1961,26 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EUR 779 902.87</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>902,87 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>902,87 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1992,12 +1990,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=779902.87, DE=902.87, LV=902.87</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2006,26 +2004,26 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EUR 389 951.44</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>952,44 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>951,44 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2035,12 +2033,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=389951.44, DE=952.44, LV=951.44</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2049,26 +2047,26 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EUR 155 980.57</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>980,57 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>980,57 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2078,12 +2076,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=155980.57, DE=980.57, LV=980.57</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2092,26 +2090,26 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EUR 155 980.57</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>980,57 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>980,57 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2121,12 +2119,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=155980.57, DE=980.57, LV=980.57</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2135,26 +2133,26 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EUR 77 990.29</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>990,29 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>990,39 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2164,12 +2162,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=77990.29, DE=990.29, LV=990.39</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2178,26 +2176,26 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EUR 779 902.97</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>902,87 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>902,87 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2207,12 +2205,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=779902.97, DE=902.87, LV=902.87</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2221,26 +2219,26 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EUR 16 636</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>636,00 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>636 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2250,12 +2248,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=16636.0, DE=636.0, LV=636.0</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2264,26 +2262,26 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EUR 8 318</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>318 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>318 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2293,12 +2291,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=8318.0, DE=318.0, LV=318.0</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2307,26 +2305,26 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EUR 3 327.20</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>327,20 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>327,20 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2336,12 +2334,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=3327.2, DE=327.2, LV=327.2</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2350,26 +2348,26 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EUR 3 327.20</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>327,20 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>327,20 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2379,12 +2377,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=3327.2, DE=327.2, LV=327.2</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2393,26 +2391,26 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EUR 1 663.60</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>663,60 Eur</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>663,60 EUR</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MONETARY_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2422,12 +2420,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Monetary amounts differ: EN=1663.6, DE=663.6, LV=663.6</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2436,16 +2434,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Article 56 o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Art. 56 d</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2455,7 +2453,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2465,12 +2463,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2479,16 +2477,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Article 163 o</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Art. 163 d</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2498,7 +2496,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2508,12 +2506,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2522,16 +2520,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>ECLI:C:2024:52</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2541,7 +2539,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2551,12 +2549,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2565,16 +2563,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>(EU, Euratom) 2024/2509</t>
+          <t>PRESENT</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>(EU, Euratom) 2024/2509</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2584,7 +2582,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MISSING_VALUE</t>
+          <t>MISSING_PARAGRAPH</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2594,12 +2592,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Legal reference present in some languages but missing in others</t>
+          <t>Paragraph missing in de, lv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -2608,41 +2606,6663 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>61</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>62</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>63</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>64</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>65</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>66</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
         <v>67</v>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>(EU, Euratom) No 883/2013</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>(EU, Euratom) Nr. 883/2013</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>MISSING_VALUE</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Legal reference present in some languages but missing in others</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>0.95</t>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>68</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>69</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>70</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Paragraph missing in de, lv</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>9</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>10</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>11</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>12</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>13</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>14</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>15</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>16</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>17</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>18</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>19</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>20</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>21</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>22</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>23</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>24</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>25</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>26</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>27</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>28</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>29</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>30</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="n">
+        <v>31</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
+        <v>32</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="n">
+        <v>33</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="n">
+        <v>34</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="n">
+        <v>35</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="n">
+        <v>36</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="n">
+        <v>37</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="n">
+        <v>38</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="n">
+        <v>39</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="n">
+        <v>40</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="n">
+        <v>41</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="n">
+        <v>42</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="n">
+        <v>43</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="n">
+        <v>44</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="n">
+        <v>45</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>46</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="n">
+        <v>47</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="n">
+        <v>48</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="n">
+        <v>49</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="n">
+        <v>50</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>51</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="n">
+        <v>52</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>53</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>54</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>55</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="n">
+        <v>56</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="n">
+        <v>57</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>58</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="n">
+        <v>61</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="n">
+        <v>62</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="n">
+        <v>63</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="n">
+        <v>64</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="n">
+        <v>65</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>66</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>67</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>68</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>69</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>70</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, lv</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>2</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>4</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>5</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>6</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>7</v>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>8</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>9</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>10</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>11</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>12</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>13</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>14</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>15</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>16</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>17</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>18</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>19</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>20</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>21</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>22</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>23</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>24</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>25</v>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>26</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>27</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>28</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>29</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>30</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>31</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>32</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>33</v>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>34</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>35</v>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>36</v>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>37</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>38</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="n">
+        <v>39</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="n">
+        <v>40</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="n">
+        <v>41</v>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>42</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="n">
+        <v>43</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="n">
+        <v>44</v>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="n">
+        <v>45</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="n">
+        <v>46</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="n">
+        <v>47</v>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="n">
+        <v>48</v>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="n">
+        <v>49</v>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>50</v>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>51</v>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>52</v>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>53</v>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>54</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>55</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>56</v>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>57</v>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>58</v>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>61</v>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>62</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>63</v>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>64</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>65</v>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>66</v>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>67</v>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>68</v>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>69</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>70</v>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>MISSING_PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Paragraph missing in en, de</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1.00</t>
         </is>
       </c>
     </row>
